--- a/files/Watchlist_Syarikat_Efek.xlsx
+++ b/files/Watchlist_Syarikat_Efek.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master List" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,25 +26,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00707070"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00707070"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,10 +59,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,20 +77,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,14 +477,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -464,112 +500,1736 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Filename: Watchlist_Syarikat_Efek.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: Watchlist_Syarikat_Efek.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FY2026 Plan</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Last reviewed</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (MYR M)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2150</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2480</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ML-0001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Pacific Industries Sdn Bhd (01)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (MYR M)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>312</v>
-      </c>
-      <c r="C6" t="n">
-        <v>378</v>
-      </c>
-      <c r="D6" t="n">
-        <v>435</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ML-0002</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Apex Holdings Sdn Bhd (02)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>MY-North</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Top performer this period</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ML-0003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Asianova Ventures Sdn Bhd (03)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Renewal next quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ML-0004</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Centralia Group Sdn Bhd (04)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>MY-East</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Renewal next quarter</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Placeholder file used by the Zava Conglomerate Copilot Demo Hub. Replace with the actual workbook before live use.</t>
+          <t>ML-0005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Northwind Logistics Sdn Bhd (05)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>MY-South</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ML-0006</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Sterling Distribution Sdn Bhd (06)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>MY-North</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ML-0007</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Meridian Services Sdn Bhd (07)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ML-0008</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Atlas Manufacturing Sdn Bhd (08)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>MY-East</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ML-0009</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Concord Energy Sdn Bhd (09)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ML-0010</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Crescent Materials Sdn Bhd (10)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ML-0011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sapphire Trading Sdn Bhd (11)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ML-0012</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Horizon Properties Sdn Bhd (12)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>ID-Surabaya</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ML-0013</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Vanguard Capital Sdn Bhd (13)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ML-0014</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Beacon Technologies Sdn Bhd (14)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ML-0015</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Crestline Resources Sdn Bhd (15)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>MY-North</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ML-0016</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Pacific Industries Sdn Bhd (16)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ML-0017</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Apex Holdings Sdn Bhd (17)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ML-0018</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Asianova Ventures Sdn Bhd (18)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>ID-Surabaya</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Top performer this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ML-0019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Centralia Group Sdn Bhd (19)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MY-South</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>ML-0020</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Northwind Logistics Sdn Bhd (20)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>MY-North</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Renewal next quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ML-0021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Distribution Sdn Bhd (21)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Renewal next quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ML-0022</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Meridian Services Sdn Bhd (22)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ML-0023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Atlas Manufacturing Sdn Bhd (23)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Daichi</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>MY-Central</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ML-0024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Concord Energy Sdn Bhd (24)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Top performer this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ML-0025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Crescent Materials Sdn Bhd (25)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Top performer this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ML-0026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Sapphire Trading Sdn Bhd (26)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>MY-East</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ML-0027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Horizon Properties Sdn Bhd (27)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ML-0028</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Vanguard Capital Sdn Bhd (28)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ML-0029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Beacon Technologies Sdn Bhd (29)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>MY-South</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>ML-0030</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Crestline Resources Sdn Bhd (30)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>ID-Jakarta</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ML-0031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Pacific Industries Sdn Bhd (31)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>MY-Central</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Top performer this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>ML-0032</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Apex Holdings Sdn Bhd (32)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Renewal next quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ML-0033</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Asianova Ventures Sdn Bhd (33)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>MY-North</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ML-0034</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Centralia Group Sdn Bhd (34)</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>MY-North</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ML-0035</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Northwind Logistics Sdn Bhd (35)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>ML-0036</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Sterling Distribution Sdn Bhd (36)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>ID-Medan</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Standing review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ML-0037</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Meridian Services Sdn Bhd (37)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>ID-Surabaya</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>ML-0038</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Atlas Manufacturing Sdn Bhd (38)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>MY-Central</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Renewal next quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ML-0039</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Concord Energy Sdn Bhd (39)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Hadar</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>ID-Medan</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Performance on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>ML-0040</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Crescent Materials Sdn Bhd (40)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>ID-Medan</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting documentation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
